--- a/dummy_experience_access_import_email.xlsx
+++ b/dummy_experience_access_import_email.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Placement_cp\placement_com\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PCP\Placement-community-portal-adv\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{981D9F9A-F1E7-4F73-836C-B99576811203}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7A4F8A6-ED97-4BBB-9B8D-2B4C35181F55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="32">
   <si>
     <t>Student Name</t>
   </si>
@@ -40,9 +40,6 @@
     <t>Total Rounds</t>
   </si>
   <si>
-    <t/>
-  </si>
-  <si>
     <t>Selected</t>
   </si>
   <si>
@@ -68,6 +65,57 @@
   </si>
   <si>
     <t>manmathan.cb23@bitsathy.ac.in</t>
+  </si>
+  <si>
+    <t>Gowtham S</t>
+  </si>
+  <si>
+    <t>sgowtham.cs23@bitsathy.ac.in</t>
+  </si>
+  <si>
+    <t>7376231CB135</t>
+  </si>
+  <si>
+    <t>7376232IT190</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ajay K p </t>
+  </si>
+  <si>
+    <t>ajay.cs23@bitsathy.ac.in</t>
+  </si>
+  <si>
+    <t>7376231cs109</t>
+  </si>
+  <si>
+    <t>placed</t>
+  </si>
+  <si>
+    <t>dhivinesh K</t>
+  </si>
+  <si>
+    <t>dhivinesh.cs23@bitsathy.ac.in</t>
+  </si>
+  <si>
+    <t>7376231CS145</t>
+  </si>
+  <si>
+    <t>Company</t>
+  </si>
+  <si>
+    <t>Mr cooper</t>
+  </si>
+  <si>
+    <t>juspay</t>
+  </si>
+  <si>
+    <t>Blue gardian</t>
+  </si>
+  <si>
+    <t>the5ers</t>
+  </si>
+  <si>
+    <t>tradingpit</t>
   </si>
 </sst>
 </file>
@@ -455,10 +503,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F6"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:G6"/>
+  <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="12.58203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.4140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.75" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.1640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.58203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.33203125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -477,66 +534,136 @@
       <c r="F1" t="s">
         <v>5</v>
       </c>
+      <c r="G1" t="s">
+        <v>26</v>
+      </c>
     </row>
-    <row r="2" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2" t="s">
+        <v>7</v>
+      </c>
+      <c r="F2" t="s">
+        <v>7</v>
+      </c>
+      <c r="G2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
         <v>13</v>
       </c>
-      <c r="B2" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C2" t="s">
+      <c r="B3" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G3" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" t="s">
+        <v>8</v>
+      </c>
+      <c r="D4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E4">
+        <v>4</v>
+      </c>
+      <c r="F4">
+        <v>4</v>
+      </c>
+      <c r="G4" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C5" t="s">
+        <v>21</v>
+      </c>
+      <c r="D5" t="s">
+        <v>22</v>
+      </c>
+      <c r="E5">
+        <v>4</v>
+      </c>
+      <c r="F5">
+        <v>4</v>
+      </c>
+      <c r="G5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>23</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C6" t="s">
+        <v>25</v>
+      </c>
+      <c r="D6" t="s">
         <v>6</v>
       </c>
-      <c r="D2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
-        <v>14</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="C3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D3" t="s">
-        <v>10</v>
-      </c>
-      <c r="E3" t="s">
-        <v>11</v>
-      </c>
-      <c r="F3" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" ht="15.5" x14ac:dyDescent="0.35"/>
-    <row r="5" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="C5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="C6" t="s">
-        <v>6</v>
+      <c r="E6">
+        <v>3</v>
+      </c>
+      <c r="F6">
+        <v>3</v>
+      </c>
+      <c r="G6" t="s">
+        <v>31</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="B2" r:id="rId1" xr:uid="{74022CA3-BF4E-495C-963E-D106BB00E5E7}"/>
     <hyperlink ref="B3" r:id="rId2" xr:uid="{6B0FC537-8164-4F15-94A4-78F2B566E63A}"/>
+    <hyperlink ref="B4" r:id="rId3" xr:uid="{8312FCE8-0FDB-4926-A638-4109A12721E2}"/>
+    <hyperlink ref="B5" r:id="rId4" xr:uid="{6704B57D-0F69-447F-97B2-022C99D66A25}"/>
+    <hyperlink ref="B6" r:id="rId5" xr:uid="{7443BCC0-0346-4709-B430-87AEA1A477CD}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:F1 C2:F2 C6 C5 C3:F3" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:F1 D2:F2 D3:F3" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>